--- a/vse-loti/341177171/spec-341177171.xlsx
+++ b/vse-loti/341177171/spec-341177171.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -95,6 +95,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -463,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1514,7 +1517,7 @@
         <v>28</v>
       </c>
       <c r="G30" s="8" t="n">
-        <v>4958900.04</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="31">
@@ -1527,19 +1530,26 @@
         <v>1500000</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>В позициях — единичные расценки за единицу измерения, а не объёмы закупки (сумма расценок 4 958 900.04 ₽ превышает НМЦК). Фактический объём в документации не раскрыт; в ИТОГО — НМЦК.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>Источник: Извещение о закупке № 32616397015.htm
 НМДЦ трубы.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35"/>
+    <row r="36"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A33:B35"/>
+    <mergeCell ref="A34:B36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
